--- a/EKG_Kalite_Yönetim_Sistemi/02_Proje ve Ürün-Proses Yeterliliği/02_CMG2 - PPQ, PPAP, Ekipman ve Tier-2/EKG-PRJ-PLN-05_proses_dogrulama_ve_gecerli_kilma_plani_urun_ekipman_ka.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/02_Proje ve Ürün-Proses Yeterliliği/02_CMG2 - PPQ, PPAP, Ekipman ve Tier-2/EKG-PRJ-PLN-05_proses_dogrulama_ve_gecerli_kilma_plani_urun_ekipman_ka.xlsx
@@ -1074,7 +1074,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-PLN-05&amp;C&amp;"Arial,Regular"&amp;11Proses Doğrulama ve Geçerli Kılma Planı (ürün, ekipman, kapasite ve kontrol)</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 02.06.2026 | Revizyon: 02.09.2026
+Revizyon nedeni: Mevcut doğrulama kapsamı korundu; kapasite planının dönem/duruş tanımı sonuç raporuyla eşleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0beff8dfadb4138"/>
   <x:tableParts count="1">
@@ -1426,7 +1427,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-PLN-05&amp;C&amp;"Arial,Regular"&amp;11Proses Doğrulama ve Geçerli Kılma Planı (ürün, ekipman, kapasite ve kontrol)</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 02.06.2026 | Revizyon: 02.09.2026
+Revizyon nedeni: Mevcut doğrulama kapsamı korundu; kapasite planının dönem/duruş tanımı sonuç raporuyla eşleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0864d3880ac14d5a"/>
   <x:tableParts count="1">
@@ -1800,7 +1802,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-PLN-05&amp;C&amp;"Arial,Regular"&amp;11Proses Doğrulama ve Geçerli Kılma Planı (ürün, ekipman, kapasite ve kontrol)</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 02.06.2026 | Revizyon: 02.09.2026
+Revizyon nedeni: Mevcut doğrulama kapsamı korundu; kapasite planının dönem/duruş tanımı sonuç raporuyla eşleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9015769db4274589"/>
   <x:tableParts count="1">
